--- a/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-2c9e9f63.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
